--- a/Padrao/Leiautes/Tabela de Preços/Tabelas Genericas/GERAL/RELACIONAMENTO - PRECOGERAL - PRECOTABELAGENERICA.xlsx
+++ b/Padrao/Leiautes/Tabela de Preços/Tabelas Genericas/GERAL/RELACIONAMENTO - PRECOGERAL - PRECOTABELAGENERICA.xlsx
@@ -626,7 +626,8 @@
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
